--- a/Independent project/Final_project/Nutrient_Summaries.xlsx
+++ b/Independent project/Final_project/Nutrient_Summaries.xlsx
@@ -811,7 +811,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>23.144</v>
@@ -820,7 +820,7 @@
         <v>57.139</v>
       </c>
       <c r="E2" t="n">
-        <v>144.754891417734</v>
+        <v>144.755839734471</v>
       </c>
       <c r="F2" t="n">
         <v>133.369</v>
@@ -837,7 +837,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>48.98625</v>
@@ -846,7 +846,7 @@
         <v>98.7295</v>
       </c>
       <c r="E3" t="n">
-        <v>211.872860701107</v>
+        <v>211.874705719557</v>
       </c>
       <c r="F3" t="n">
         <v>213.541</v>
@@ -915,7 +915,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>41.8645</v>
@@ -924,7 +924,7 @@
         <v>143</v>
       </c>
       <c r="E6" t="n">
-        <v>306.796180327869</v>
+        <v>306.807109289617</v>
       </c>
       <c r="F6" t="n">
         <v>354.1555</v>
